--- a/data/mema_codebook.xlsx
+++ b/data/mema_codebook.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\RabbitSnore\Documents\Projects\Misinformation_meta\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projects\Misinformation_meta\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0238BFD-0229-4D72-B989-E4900DDEB2E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{461399C6-FDAB-4B93-9577-F9D0AE1174EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{38FE1802-D0E4-4D04-A5E5-B4F66745BCD3}"/>
+    <workbookView xWindow="-3225" yWindow="-20310" windowWidth="27660" windowHeight="16110" xr2:uid="{38FE1802-D0E4-4D04-A5E5-B4F66745BCD3}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="268" uniqueCount="187">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="265" uniqueCount="186">
   <si>
     <t>id_record</t>
   </si>
@@ -305,15 +305,9 @@
     <t>DOI</t>
   </si>
   <si>
-    <t>Modality of study procedures</t>
-  </si>
-  <si>
     <t>Participant incentives for participating</t>
   </si>
   <si>
-    <t>Notes on participant incentives</t>
-  </si>
-  <si>
     <t>Indicator for whether the study was preregistered</t>
   </si>
   <si>
@@ -338,9 +332,6 @@
     <t>Type of accuracy measure for means</t>
   </si>
   <si>
-    <t>Description of sampled population</t>
-  </si>
-  <si>
     <t>Total sample size</t>
   </si>
   <si>
@@ -365,54 +356,9 @@
     <t>Maximum age of participants</t>
   </si>
   <si>
-    <t>Neurological or psychological diagnosis of the sample</t>
-  </si>
-  <si>
-    <t>mood induced in participants</t>
-  </si>
-  <si>
-    <t>Presence of warning about misinformation before the initial event</t>
-  </si>
-  <si>
-    <t>Presence of alcohol before the intial event</t>
-  </si>
-  <si>
-    <t>Medium of the initial event</t>
-  </si>
-  <si>
-    <t>Valence of the event</t>
-  </si>
-  <si>
-    <t>Presence of warning about misinformation after the initial event</t>
-  </si>
-  <si>
-    <t>Delay between exposure to event and misinformation, in hours (if less than one hour, use 0; if in days, multiply days by 24)</t>
-  </si>
-  <si>
-    <t>Method of exposure to misinformation</t>
-  </si>
-  <si>
-    <t>Manipulation of the source of misinformation</t>
-  </si>
-  <si>
-    <t>Valence of the misinformation</t>
-  </si>
-  <si>
-    <t>Delay between exposure to misinformation and recall, in hours (if less than one hour, use 0; if in days, multiply days by 24)</t>
-  </si>
-  <si>
-    <t>Presence of warning about misinformation after exposure</t>
-  </si>
-  <si>
     <t>Presence of a correction of the misinformation after exposure</t>
   </si>
   <si>
-    <t>Type of test</t>
-  </si>
-  <si>
-    <t>Medium of test</t>
-  </si>
-  <si>
     <t>values</t>
   </si>
   <si>
@@ -461,9 +407,6 @@
     <t>no_manipulation = no manipulation of valence; negative = negative mood; neutral = neutral mood; positive = positive mood</t>
   </si>
   <si>
-    <t>0 = no warning; 1 = warning</t>
-  </si>
-  <si>
     <t>0 = no correction; 1 = correction</t>
   </si>
   <si>
@@ -545,15 +488,6 @@
     <t>consistent = control items contain specific information from the original event; no_misinformation = control condition received no misleading PEI; neutral = control condition received information in general terms that was not inconsistent with the original</t>
   </si>
   <si>
-    <t>Total number of items on the test, including filler items.</t>
-  </si>
-  <si>
-    <t>Number of misled items on the test.</t>
-  </si>
-  <si>
-    <t>Number of control items on the test.</t>
-  </si>
-  <si>
     <t>Central or peripheral details. Coded only when there is an explicit manipulation of centrality.</t>
   </si>
   <si>
@@ -578,9 +512,6 @@
     <t>0 = not imputed; 1 = imputed</t>
   </si>
   <si>
-    <t>Standardized mean difference for the misinformation effect.</t>
-  </si>
-  <si>
     <t>Sampling variance for the standardized mean difference.</t>
   </si>
   <si>
@@ -597,6 +528,72 @@
   </si>
   <si>
     <t>Materials used for the initial event. Each material set was given an arbitrary but descriptive label when first coded, and this label was reused whenever a study explicitly reported using the same materials as another study (or when it could be clearly inferred that the same materials had been used across multiple studies).</t>
+  </si>
+  <si>
+    <t>Neurological or psychological diagnosis of the sample. Only coded if the study explicitly noted that the sample was recruited to include a particular population with a specified condition.</t>
+  </si>
+  <si>
+    <t>Mood induced in participants. Only coded when the study explicitly mentioned manipulating participants mood/emotions.</t>
+  </si>
+  <si>
+    <t>Presence of alcohol before the intial event. Only coded when the study explicitly noted exposure to alcohol.</t>
+  </si>
+  <si>
+    <t>Medium of the initial event. Inferred from the description provided in the study.</t>
+  </si>
+  <si>
+    <t>Valence of the event. Only coded when the study explicitly noted that the valence of the event materials was deliberate or manipulated.</t>
+  </si>
+  <si>
+    <t>Delay between exposure to event and misinformation, in hours (if less than one hour, use 0; if in days, multiply days by 24). When retention interval varied, we extracted the provided mean interval.</t>
+  </si>
+  <si>
+    <t>Delay between exposure to misinformation and recall, in hours (if less than one hour, use 0; if in days, multiply days by 24). When retention interval varied, we extracted the provided mean interval.</t>
+  </si>
+  <si>
+    <t>Medium of test. Inferred from the study's description of the test.</t>
+  </si>
+  <si>
+    <t>Type of test. Inferred from the labeling and description of the test.</t>
+  </si>
+  <si>
+    <t>Total number of items on the test, including non-critical filler items.</t>
+  </si>
+  <si>
+    <t>Number of control items on the test. Coded from explicit statements about the number of items and/or from the maximum of a count score used to measure accuracy.</t>
+  </si>
+  <si>
+    <t>Number of misled items on the test. Coded from explicit statements about the number of items and/or from the maximum of a count score used to measure accuracy.</t>
+  </si>
+  <si>
+    <t>Standardized mean difference for the misinformation effect. Calculated with Hedges's small sample bias adjustment.</t>
+  </si>
+  <si>
+    <t>Method of exposure to misinformation. Extracted for descriptive purposes.</t>
+  </si>
+  <si>
+    <t>Manipulation of the source of misinformation. Coded only when the study explicitly noted a manipulation of source credibility or expertise.</t>
+  </si>
+  <si>
+    <t>Valence of the misinformation. Only coded when the study explicitly noted that the valence of the PEI was deliberate or manipulated.</t>
+  </si>
+  <si>
+    <t>Count of warnings about misinformation after exposure.</t>
+  </si>
+  <si>
+    <t>Count of warnings about misinformation after event.</t>
+  </si>
+  <si>
+    <t>Count of warnings about misinformation prior to the event.</t>
+  </si>
+  <si>
+    <t>Notes on participant incentives. Provides additional information about how incentives were described.</t>
+  </si>
+  <si>
+    <t>Modality of study procedures. Inferred from description of procedures.</t>
+  </si>
+  <si>
+    <t>Description of sampled population. Inferred from description of recruited sample.</t>
   </si>
 </sst>
 </file>
@@ -976,13 +973,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8EDF0301-BBC4-4423-AE5D-86F2CEAC869C}">
   <dimension ref="A1:D80"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="22.73046875" customWidth="1"/>
+    <col min="1" max="1" width="22.7109375" customWidth="1"/>
     <col min="2" max="2" width="37" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>73</v>
       </c>
@@ -990,13 +987,13 @@
         <v>74</v>
       </c>
       <c r="C1" t="s">
-        <v>126</v>
+        <v>108</v>
       </c>
       <c r="D1" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.45">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -1004,10 +1001,10 @@
         <v>75</v>
       </c>
       <c r="C2" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.45">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -1015,10 +1012,10 @@
         <v>77</v>
       </c>
       <c r="C3" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.45">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>2</v>
       </c>
@@ -1026,10 +1023,10 @@
         <v>78</v>
       </c>
       <c r="C4" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.45">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -1037,10 +1034,10 @@
         <v>79</v>
       </c>
       <c r="C5" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.45">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>4</v>
       </c>
@@ -1048,10 +1045,10 @@
         <v>76</v>
       </c>
       <c r="C6" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.45">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>5</v>
       </c>
@@ -1059,10 +1056,10 @@
         <v>80</v>
       </c>
       <c r="C7" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.45">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>6</v>
       </c>
@@ -1070,10 +1067,10 @@
         <v>81</v>
       </c>
       <c r="C8" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.45">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>7</v>
       </c>
@@ -1081,10 +1078,10 @@
         <v>82</v>
       </c>
       <c r="C9" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.45">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>8</v>
       </c>
@@ -1092,10 +1089,10 @@
         <v>83</v>
       </c>
       <c r="C10" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.45">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>9</v>
       </c>
@@ -1103,10 +1100,10 @@
         <v>84</v>
       </c>
       <c r="C11" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.45">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>10</v>
       </c>
@@ -1114,10 +1111,10 @@
         <v>85</v>
       </c>
       <c r="C12" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.45">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>11</v>
       </c>
@@ -1125,10 +1122,10 @@
         <v>86</v>
       </c>
       <c r="C13" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.45">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>12</v>
       </c>
@@ -1136,10 +1133,10 @@
         <v>87</v>
       </c>
       <c r="C14" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.45">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>13</v>
       </c>
@@ -1147,803 +1144,794 @@
         <v>88</v>
       </c>
       <c r="C15" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.45">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>156</v>
+        <v>137</v>
       </c>
       <c r="C16" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.45">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>157</v>
+        <v>138</v>
       </c>
       <c r="C17" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.45">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>16</v>
       </c>
       <c r="B18" t="s">
-        <v>158</v>
+        <v>139</v>
       </c>
       <c r="C18" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.45">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>17</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>100</v>
+        <v>185</v>
       </c>
       <c r="C19" t="s">
-        <v>127</v>
+        <v>109</v>
       </c>
       <c r="D19" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.45">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>18</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>89</v>
+        <v>184</v>
       </c>
       <c r="C20" t="s">
-        <v>127</v>
+        <v>109</v>
       </c>
       <c r="D20" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.45">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>19</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C21" t="s">
-        <v>127</v>
+        <v>109</v>
       </c>
       <c r="D21" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.45">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>20</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>91</v>
+        <v>183</v>
       </c>
       <c r="C22" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.45">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>21</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="C23" t="s">
-        <v>128</v>
+        <v>110</v>
       </c>
       <c r="D23" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.45">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>22</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="C24" t="s">
-        <v>128</v>
+        <v>110</v>
       </c>
       <c r="D24" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.45">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>23</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C25" t="s">
-        <v>128</v>
+        <v>110</v>
       </c>
       <c r="D25" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.45">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>24</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="C26" t="s">
-        <v>128</v>
+        <v>110</v>
       </c>
       <c r="D26" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.45">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>25</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C27" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.45">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>26</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C28" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.45">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>27</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="C29" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.45">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>28</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="C30" t="s">
-        <v>127</v>
+        <v>109</v>
       </c>
       <c r="D30" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.45">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>29</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>160</v>
+        <v>141</v>
       </c>
       <c r="C31" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.45">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>30</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>159</v>
+        <v>140</v>
       </c>
       <c r="C32" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.45">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>31</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>161</v>
+        <v>142</v>
       </c>
       <c r="C33" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.45">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>32</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>162</v>
+        <v>143</v>
       </c>
       <c r="C34" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.45">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>33</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>163</v>
+        <v>144</v>
       </c>
       <c r="C35" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.45">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>34</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>164</v>
+        <v>145</v>
       </c>
       <c r="C36" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.45">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>35</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C37" t="s">
-        <v>128</v>
+        <v>110</v>
       </c>
       <c r="D37" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.45">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>36</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>182</v>
+        <v>159</v>
       </c>
       <c r="C38" t="s">
-        <v>128</v>
+        <v>110</v>
       </c>
       <c r="D38" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.45">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>37</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>183</v>
+        <v>160</v>
       </c>
       <c r="C39" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.45">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>38</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>166</v>
+        <v>147</v>
       </c>
       <c r="C40" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.45">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>39</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>184</v>
+        <v>161</v>
       </c>
       <c r="C41" t="s">
-        <v>127</v>
+        <v>109</v>
       </c>
       <c r="D41" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.45">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>40</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="C42" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.45">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>41</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C43" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.45">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>42</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="C44" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.45">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>43</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="C45" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.45">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>44</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="C46" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.45">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>45</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="C47" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.45">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>46</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="C48" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.45">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>47</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>185</v>
+        <v>162</v>
       </c>
       <c r="C49" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.45">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>48</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>109</v>
+        <v>164</v>
       </c>
       <c r="C50" t="s">
-        <v>127</v>
+        <v>109</v>
       </c>
       <c r="D50" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.45">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>49</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>110</v>
+        <v>165</v>
       </c>
       <c r="C51" t="s">
-        <v>127</v>
+        <v>109</v>
       </c>
       <c r="D51" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.45">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>50</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>111</v>
+        <v>182</v>
       </c>
       <c r="C52" t="s">
-        <v>128</v>
-      </c>
-      <c r="D52" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.45">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>51</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>112</v>
+        <v>166</v>
       </c>
       <c r="C53" t="s">
-        <v>128</v>
+        <v>110</v>
       </c>
       <c r="D53" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.45">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>52</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>113</v>
+        <v>167</v>
       </c>
       <c r="C54" t="s">
-        <v>127</v>
+        <v>109</v>
       </c>
       <c r="D54" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.45">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>53</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>186</v>
+        <v>163</v>
       </c>
       <c r="C55" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.45">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>54</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>114</v>
+        <v>168</v>
       </c>
       <c r="C56" t="s">
-        <v>127</v>
+        <v>109</v>
       </c>
       <c r="D56" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.45">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>55</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>167</v>
+        <v>148</v>
       </c>
       <c r="C57" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.45">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>56</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>115</v>
+        <v>181</v>
       </c>
       <c r="C58" t="s">
-        <v>128</v>
-      </c>
-      <c r="D58" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.45">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>57</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>116</v>
+        <v>169</v>
       </c>
       <c r="C59" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.45">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>58</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>136</v>
+        <v>118</v>
       </c>
       <c r="C60" t="s">
-        <v>127</v>
+        <v>109</v>
       </c>
       <c r="D60" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.45">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>59</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>117</v>
+        <v>177</v>
       </c>
       <c r="C61" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.45">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>60</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>118</v>
+        <v>178</v>
       </c>
       <c r="C62" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.45">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>61</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>119</v>
+        <v>179</v>
       </c>
       <c r="C63" t="s">
+        <v>109</v>
+      </c>
+      <c r="D63" t="s">
         <v>127</v>
       </c>
-      <c r="D63" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.45">
+    </row>
+    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>62</v>
       </c>
       <c r="B64" t="s">
-        <v>147</v>
+        <v>128</v>
       </c>
       <c r="C64" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.45">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>63</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>120</v>
+        <v>170</v>
       </c>
       <c r="C65" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.45">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>64</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>121</v>
+        <v>180</v>
       </c>
       <c r="C66" t="s">
-        <v>128</v>
-      </c>
-      <c r="D66" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.45">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>65</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>122</v>
+        <v>106</v>
       </c>
       <c r="C67" t="s">
-        <v>128</v>
+        <v>110</v>
       </c>
       <c r="D67" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.45">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>66</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>123</v>
+        <v>172</v>
       </c>
       <c r="C68" t="s">
-        <v>127</v>
+        <v>109</v>
       </c>
       <c r="D68" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.45">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>67</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>124</v>
+        <v>171</v>
       </c>
       <c r="C69" t="s">
-        <v>127</v>
+        <v>109</v>
       </c>
       <c r="D69" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.45">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>68</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>172</v>
+        <v>150</v>
       </c>
       <c r="C70" t="s">
-        <v>127</v>
+        <v>109</v>
       </c>
       <c r="D70" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.45">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>69</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="C71" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.45">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>70</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="C72" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.45">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>71</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="C73" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.45">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>72</v>
       </c>
       <c r="B74" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="C74" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>131</v>
+      </c>
+      <c r="B75" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="C75" t="s">
+        <v>109</v>
+      </c>
+      <c r="D75" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>132</v>
+      </c>
+      <c r="B76" t="s">
+        <v>133</v>
+      </c>
+      <c r="C76" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="77" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>151</v>
+      </c>
+      <c r="B77" t="s">
+        <v>156</v>
+      </c>
+      <c r="C77" t="s">
+        <v>110</v>
+      </c>
+      <c r="D77" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="78" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>152</v>
+      </c>
+      <c r="B78" t="s">
+        <v>176</v>
+      </c>
+      <c r="C78" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="79" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>153</v>
+      </c>
+      <c r="B79" t="s">
+        <v>158</v>
+      </c>
+      <c r="C79" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="80" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>154</v>
+      </c>
+      <c r="B80" t="s">
         <v>155</v>
       </c>
-      <c r="C74" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A75" t="s">
-        <v>150</v>
-      </c>
-      <c r="B75" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="C75" t="s">
-        <v>127</v>
-      </c>
-      <c r="D75" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A76" t="s">
-        <v>151</v>
-      </c>
-      <c r="B76" t="s">
-        <v>152</v>
-      </c>
-      <c r="C76" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A77" t="s">
-        <v>173</v>
-      </c>
-      <c r="B77" t="s">
-        <v>178</v>
-      </c>
-      <c r="C77" t="s">
-        <v>128</v>
-      </c>
-      <c r="D77" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A78" t="s">
-        <v>174</v>
-      </c>
-      <c r="B78" t="s">
-        <v>180</v>
-      </c>
-      <c r="C78" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A79" t="s">
-        <v>175</v>
-      </c>
-      <c r="B79" t="s">
-        <v>181</v>
-      </c>
-      <c r="C79" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A80" t="s">
-        <v>176</v>
-      </c>
-      <c r="B80" t="s">
-        <v>177</v>
-      </c>
       <c r="C80" t="s">
-        <v>128</v>
+        <v>110</v>
       </c>
     </row>
   </sheetData>

--- a/data/mema_codebook.xlsx
+++ b/data/mema_codebook.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projects\Misinformation_meta\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{461399C6-FDAB-4B93-9577-F9D0AE1174EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E211955A-CDBE-4F1C-BF4C-7F659A1F4781}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-3225" yWindow="-20310" windowWidth="27660" windowHeight="16110" xr2:uid="{38FE1802-D0E4-4D04-A5E5-B4F66745BCD3}"/>
+    <workbookView xWindow="780" yWindow="-18915" windowWidth="28800" windowHeight="15345" xr2:uid="{38FE1802-D0E4-4D04-A5E5-B4F66745BCD3}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1252,13 +1252,13 @@
         <v>22</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C24" t="s">
         <v>110</v>
       </c>
       <c r="D24" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
@@ -1266,13 +1266,13 @@
         <v>23</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C25" t="s">
         <v>110</v>
       </c>
       <c r="D25" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
